--- a/Files/AlbumStockESA.xlsx
+++ b/Files/AlbumStockESA.xlsx
@@ -626,7 +626,7 @@
         <v>Pilsener Game 5</v>
       </c>
       <c r="D10" t="str">
-        <v>https://mysiterobert.s3.us-east-1.amazonaws.com/BEES_2026/Album2026/ESA/ESA_PilsenerStickerGame5_200+Points.png</v>
+        <v>https://mysiterobert.s3.us-east-1.amazonaws.com/BEES_2026/Album2026/ESA/ESA_PilsenerStickerGame5_200Points.png</v>
       </c>
       <c r="E10">
         <v>200</v>
@@ -649,7 +649,7 @@
         <v>Pilsener Game 6</v>
       </c>
       <c r="D11" t="str">
-        <v>https://mysiterobert.s3.us-east-1.amazonaws.com/BEES_2026/Album2026/ESA/ESA_PilsenerStickerGame6_200+Points.png</v>
+        <v>https://mysiterobert.s3.us-east-1.amazonaws.com/BEES_2026/Album2026/ESA/ESA_PilsenerStickerGame6_200Points.png</v>
       </c>
       <c r="E11">
         <v>200</v>
@@ -764,7 +764,7 @@
         <v>Michelob Ultra Game 7 - No Prize</v>
       </c>
       <c r="D16" t="str">
-        <v>https://mysiterobert.s3.us-east-1.amazonaws.com/BEES_2026/Album2026/ESA/ESA_MU+StickerGame7_Non-Prize.png</v>
+        <v>https://mysiterobert.s3.us-east-1.amazonaws.com/BEES_2026/Album2026/ESA/ESA_MU+StickerGame6_Non-Prize.png</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>Michelob Ultra Game 8 - No Prize</v>
       </c>
       <c r="D17" t="str">
-        <v>https://mysiterobert.s3.us-east-1.amazonaws.com/BEES_2026/Album2026/ESA/ESA_MU+StickerGame8_Non-prize.png</v>
+        <v>https://mysiterobert.s3.us-east-1.amazonaws.com/BEES_2026/Album2026/ESA/ESA_MU+StickerGame7_Non-prize.png</v>
       </c>
       <c r="E17">
         <v>0</v>
